--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260907.xlsx
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>18,948,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,948,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
